--- a/data/availability/projects/mountain-view/mountain-view-aliva.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-aliva.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -909,7 +909,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -942,7 +941,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -966,7 +965,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -999,7 +997,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1023,7 +1021,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1080,7 +1077,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1137,7 +1133,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1194,7 +1189,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1251,7 +1245,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1308,7 +1301,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1365,7 +1357,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1422,7 +1413,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1455,7 +1445,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1479,7 +1469,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1536,7 +1525,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1593,7 +1581,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1650,7 +1637,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1707,7 +1693,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
